--- a/incident_report_forms/035_fire_alarm_incident_form--incident_report_forms.xlsx
+++ b/incident_report_forms/035_fire_alarm_incident_form--incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_3.1,_'name':_'test'}</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 3.1, 'name': 'Test'}</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_3.1,_'name':_'test'}</t>
+          <t>smoke_detector</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 3.1, 'name': 'Test'}</t>
+          <t>Smoke Detector</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3.2,_'name':_'smoke_detector'}</t>
+          <t>fire_alarm_panel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3.2, 'name': 'Smoke Detector'}</t>
+          <t>Fire Alarm Panel</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_3.3,_'name':_'fire_alarm_panel'}</t>
+          <t>emergency_exit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 3.3, 'name': 'Fire Alarm Panel'}</t>
+          <t>Emergency Exit</t>
         </is>
       </c>
     </row>
@@ -1199,29 +1199,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3.4,_'name':_'emergency_exit'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3.4, 'name': 'Emergency Exit'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>alarm_type_choices</t>
+          <t>alarm_level_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3.5,_'name':_'other'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3.5, 'name': 'Other'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_6.1,_'name':_'low'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 6.1, 'name': 'Low'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_6.2,_'name':_'medium'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 6.2, 'name': 'Medium'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>alarm_level_choices</t>
+          <t>alarm_source_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6.3,_'name':_'high'}</t>
+          <t>fire_alarm_panel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6.3, 'name': 'High'}</t>
+          <t>Fire Alarm Panel</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7.1,_'name':_'fire_alarm_panel'}</t>
+          <t>emergency_exit</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7.1, 'name': 'Fire Alarm Panel'}</t>
+          <t>Emergency Exit</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1301,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_7.2,_'name':_'emergency_exit'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 7.2, 'name': 'Emergency Exit'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>alarm_source_choices</t>
+          <t>fire_fighting_method_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_7.3,_'name':_'other'}</t>
+          <t>fire_extinguisher</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 7.3, 'name': 'Other'}</t>
+          <t>Fire Extinguisher</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_9.1,_'name':_'fire_extinguisher'}</t>
+          <t>foam</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 9.1, 'name': 'Fire Extinguisher'}</t>
+          <t>Foam</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_9.2,_'name':_'fire_extinguisher'}</t>
+          <t>fire_blanket</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 9.2, 'name': 'Fire Extinguisher'}</t>
+          <t>Fire Blanket</t>
         </is>
       </c>
     </row>
@@ -1369,46 +1369,46 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_9.3,_'name':_'foam'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 9.3, 'name': 'Foam'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fire_fighting_method_choices</t>
+          <t>cause_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_9.4,_'name':_'fire_blanket'}</t>
+          <t>system_test</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 9.4, 'name': 'Fire Blanket'}</t>
+          <t>System Test</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fire_fighting_method_choices</t>
+          <t>cause_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_9.5,_'name':_'other'}</t>
+          <t>human_error</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 9.5, 'name': 'Other'}</t>
+          <t>Human Error</t>
         </is>
       </c>
     </row>
@@ -1420,46 +1420,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_10.1,_'name':_'system_test'}</t>
+          <t>equipment_failure</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 10.1, 'name': 'System Test'}</t>
+          <t>Equipment Failure</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cause_choices</t>
+          <t>fire_extinguisher_location_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_10.2,_'name':_'human_error'}</t>
+          <t>near_fire_alarm_panel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 10.2, 'name': 'Human Error'}</t>
+          <t>Near Fire Alarm Panel</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cause_choices</t>
+          <t>fire_extinguisher_location_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_10.3,_'name':_'equipment_failure'}</t>
+          <t>near_fire_exit</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 10.3, 'name': 'Equipment Failure'}</t>
+          <t>Near Fire Exit</t>
         </is>
       </c>
     </row>
@@ -1471,46 +1471,46 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_14.1,_'name':_'near_fire_alarm_panel'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 14.1, 'name': 'Near Fire Alarm Panel'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fire_extinguisher_location_choices</t>
+          <t>evacuation_procedure_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_14.2,_'name':_'near_fire_exit'}</t>
+          <t>evacuation_by_elevator</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 14.2, 'name': 'Near Fire Exit'}</t>
+          <t>Evacuation by Elevator</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>fire_extinguisher_location_choices</t>
+          <t>evacuation_procedure_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_14.3,_'name':_'other'}</t>
+          <t>evacuation_by_stairs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 14.3, 'name': 'Other'}</t>
+          <t>Evacuation by Stairs</t>
         </is>
       </c>
     </row>
@@ -1522,46 +1522,46 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_15.1,_'name':_'evacuation_by_elevator'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 15.1, 'name': 'Evacuation by Elevator'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>evacuation_procedure_choices</t>
+          <t>evacuation_procedure_effectiveness_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_15.2,_'name':_'evacuation_by_stairs'}</t>
+          <t>effective</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 15.2, 'name': 'Evacuation by Stairs'}</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>evacuation_procedure_choices</t>
+          <t>evacuation_procedure_effectiveness_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_15.3,_'name':_'other'}</t>
+          <t>ineffective</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 15.3, 'name': 'Other'}</t>
+          <t>Ineffective</t>
         </is>
       </c>
     </row>
@@ -1573,46 +1573,46 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_21.1,_'name':_'effective'}</t>
+          <t>not_evaluated</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 21.1, 'name': 'Effective'}</t>
+          <t>Not Evaluated</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>evacuation_procedure_effectiveness_choices</t>
+          <t>incident_status_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_21.2,_'name':_'ineffective'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 21.2, 'name': 'Ineffective'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>evacuation_procedure_effectiveness_choices</t>
+          <t>incident_status_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_21.3,_'name':_'not_evaluated'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 21.3, 'name': 'Not Evaluated'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1624,46 +1624,46 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_22.1,_'name':_'open'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 22.1, 'name': 'Open'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>incident_status_choices</t>
+          <t>incident_type_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_22.2,_'name':_'closed'}</t>
+          <t>fire_alarm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 22.2, 'name': 'Closed'}</t>
+          <t>Fire Alarm</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>incident_status_choices</t>
+          <t>incident_type_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_22.3,_'name':_'in_progress'}</t>
+          <t>fire_extinguisher</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 22.3, 'name': 'In Progress'}</t>
+          <t>Fire Extinguisher</t>
         </is>
       </c>
     </row>
@@ -1675,46 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_23.1,_'name':_'fire_alarm'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 23.1, 'name': 'Fire Alarm'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>incident_type_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'id':_23.2,_'name':_'fire_extinguisher'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'id': 23.2, 'name': 'Fire Extinguisher'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>incident_type_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'id':_23.3,_'name':_'other'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'id': 23.3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
